--- a/inst/extdata/projects/Example/Configurations/Plots.xlsx
+++ b/inst/extdata/projects/Example/Configurations/Plots.xlsx
@@ -7,13 +7,10 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="DataCombined" sheetId="1" r:id="rId1"/>
+    <sheet name="dataCombined" sheetId="1" r:id="rId1"/>
     <sheet name="plotConfiguration" sheetId="2" r:id="rId2"/>
     <sheet name="plotGrids" sheetId="3" r:id="rId3"/>
     <sheet name="exportConfiguration" sheetId="4" r:id="rId4"/>
-    <sheet name="dataTypes" sheetId="5" r:id="rId5"/>
-    <sheet name="plotTypes" sheetId="6" r:id="rId6"/>
-    <sheet name="ObservedDataNames" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -357,7 +354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -430,7 +427,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AciclovirPVB</t>
+          <t>Aciclovir_individual</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -440,12 +437,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aciclovir simulated</t>
+          <t>Aciclovir simulated (male)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TestScenario</t>
+          <t>Aciclovir_iv</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -456,124 +453,124 @@
       <c r="G2" t="inlineStr">
         <is>
           <t>Aciclovir PVB</t>
-        </is>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>h</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AciclovirPVB</t>
+          <t>Aciclovir_individual</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>observed</t>
+          <t>simulated</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aciclovri observed</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Laskin 1982.Group A_Aciclovir_1_Human_MALE_PeripheralVenousBlood_Plasma_2.5 mg/kg_iv_</t>
+          <t>Aciclovir simulated (female)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Aciclovir_iv_female</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Organism|PeripheralVenousBlood|Aciclovir|Plasma (Peripheral Venous Blood)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Aciclovir PVB</t>
-        </is>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>min</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AciclovirPop</t>
+          <t>Aciclovir_individual</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>simulated</t>
+          <t>observed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aciclovir simulated</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PopulationScenario</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Organism|PeripheralVenousBlood|Aciclovir|Plasma (Peripheral Venous Blood)</t>
+          <t>Aciclovir observed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Laskin 1982.Group A_Aciclovir_1_Human_MALE_PeripheralVenousBlood_Plasma_2.5 mg/kg_iv_</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>AciclovirPop</t>
-        </is>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>h</t>
+          <t>Aciclovir PVB</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AciclovirPop</t>
+          <t>Aciclovir_population</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>simulated</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Aciclovir simulated</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Aciclovir_iv_population</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Organism|PeripheralVenousBlood|Aciclovir|Plasma (Peripheral Venous Blood)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Aciclovir PVB</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Aciclovir_population</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>observed</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Aciclovri observed</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Aciclovir observed</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Laskin 1982.Group A_Aciclovir_1_Human_MALE_PeripheralVenousBlood_Plasma_2.5 mg/kg_iv_</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>AciclovirPop</t>
-        </is>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>min</t>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Aciclovir PVB</t>
         </is>
       </c>
     </row>
@@ -610,57 +607,57 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>subtitle</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>xUnit</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>yUnit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>xAxisScale</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>yAxisScale</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>xValuesLimits</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>yValuesLimits</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>quantiles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>nsd</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>foldDistance</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>subtitle</t>
         </is>
       </c>
     </row>
@@ -672,7 +669,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AciclovirPVB</t>
+          <t>Aciclovir_individual</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -682,22 +679,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PlotTitle</t>
+          <t>Aciclovir IV 250 mg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>Individual time profiles</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>0, 24</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>PlotSubtitle</t>
         </is>
       </c>
     </row>
@@ -709,7 +706,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AciclovirPVB</t>
+          <t>Aciclovir_individual</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -717,7 +714,12 @@
           <t>observedVsSimulated</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Observed vs Simulated</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>2, 3</t>
         </is>
@@ -731,12 +733,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AciclovirPVB</t>
+          <t>Aciclovir_individual</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>residualsVsSimulated</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Residuals</t>
         </is>
       </c>
     </row>
@@ -748,7 +755,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AciclovirPop</t>
+          <t>Aciclovir_population</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -756,22 +763,32 @@
           <t>population</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Population simulation</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>Aciclovir IV 250 mg — 50 European adults</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>h</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>0, 24</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>arithmetic</t>
         </is>
       </c>
-      <c r="M5">
+      <c r="N5">
         <v>1.96</v>
       </c>
     </row>
@@ -810,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Aciclovir</t>
+          <t>Individual_diagnostics</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -820,19 +837,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GridTitle</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>GridSubtitle</t>
+          <t>Aciclovir — Individual Diagnostics</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Aciclovir2</t>
+          <t>Observed_vs_simulated</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -844,7 +856,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Aciclovir3</t>
+          <t>Population_time_profile</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -860,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -876,104 +888,61 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>format</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>width</t>
         </is>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>dataType</t>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>height</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>dpi</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>observed</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>simulated</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>plotType</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>individual</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>population</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>observedVsSimulated</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>residualsVsSimulated</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>residualsVsTime</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1"/>
+          <t>Individual_diagnostics</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Aciclovir_diagnostics</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>png</t>
+        </is>
+      </c>
+      <c r="D2">
+        <v>20</v>
+      </c>
+      <c r="E2">
+        <v>15</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="G2">
+        <v>300</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
